--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/git/JPEtemplate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isottavalpreda/Desktop/Replication/JPEtemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067DD2C7-24FE-2447-A5A8-8F6542C7C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5514A3D-5837-3D48-831C-B95ACE27AF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6900" yWindow="1100" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="41">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -46,6 +47,108 @@
   </si>
   <si>
     <t>In-text numbers</t>
+  </si>
+  <si>
+    <t>Code/01. Data Cleaning.R</t>
+  </si>
+  <si>
+    <t>Data/Processed/Knowledge.csv</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Data/Processed/Attitudes.csv</t>
+  </si>
+  <si>
+    <t>Data/Processed/Dif.csv</t>
+  </si>
+  <si>
+    <t>Data/Processed/behavior_long.csv</t>
+  </si>
+  <si>
+    <t>Figure 1</t>
+  </si>
+  <si>
+    <t>N/A - non-reproducible study material</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>N/A - source image</t>
+  </si>
+  <si>
+    <t>Figure 2</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>Code/02. Descriptive.R</t>
+  </si>
+  <si>
+    <t>Figure 3</t>
+  </si>
+  <si>
+    <t>Figure 4</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Code/03. Knowledge and mechanisms.R</t>
+  </si>
+  <si>
+    <t>Figure 5</t>
+  </si>
+  <si>
+    <t>Table 3</t>
+  </si>
+  <si>
+    <t>Code/04. Behavior.R</t>
+  </si>
+  <si>
+    <t>Figure 6</t>
+  </si>
+  <si>
+    <t>Table 4</t>
+  </si>
+  <si>
+    <t>Code/05. Attitudes.R</t>
+  </si>
+  <si>
+    <t>Table 5</t>
+  </si>
+  <si>
+    <t>Table 6</t>
+  </si>
+  <si>
+    <t>Table 7</t>
+  </si>
+  <si>
+    <t>Table 8</t>
+  </si>
+  <si>
+    <t>Table A.9</t>
+  </si>
+  <si>
+    <t>Figure A.7</t>
+  </si>
+  <si>
+    <t>Figure A.8</t>
+  </si>
+  <si>
+    <t>Table A.10</t>
+  </si>
+  <si>
+    <t>Table A.11</t>
+  </si>
+  <si>
+    <t>Table A.12</t>
+  </si>
+  <si>
+    <t>Table A.13</t>
   </si>
 </sst>
 </file>
@@ -89,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -97,12 +200,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -118,7 +218,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -434,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -461,46 +561,380 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>134</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>198</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>233</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>251</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>390</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>227</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>373</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>485</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>278</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <v>389</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>482</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>529</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>596</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>776</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>434</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22">
+        <v>1150</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <v>1112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>1321</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25">
+        <v>1198</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>1237</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>1449</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28">
+        <v>1040</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -508,4 +942,395 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831FA1CA-894C-B04E-B458-AAFE94F3D796}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="34.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>134</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>198</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>233</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>251</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <v>390</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>107</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>227</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>373</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17">
+        <v>485</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18">
+        <v>278</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <v>389</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20">
+        <v>482</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>529</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22">
+        <v>596</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <v>776</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24">
+        <v>434</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25">
+        <v>1150</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>1112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>1321</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28">
+        <v>1198</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>1237</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30">
+        <v>1449</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31">
+        <v>1040</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>